--- a/data/trans_camb/P1404-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1404-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,99</t>
+          <t>7,39</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,54</t>
+          <t>6,45</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6,83</t>
+          <t>7,0</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 7,13</t>
+          <t>-0,22; 7,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 7,88</t>
+          <t>0,5; 8,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,28; 10,79</t>
+          <t>4,21; 10,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 3,45</t>
+          <t>-4,89; 3,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 5,4</t>
+          <t>-2,82; 5,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 10,33</t>
+          <t>2,2; 10,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 4,05</t>
+          <t>-1,12; 4,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 5,47</t>
+          <t>0,13; 5,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,19; 9,43</t>
+          <t>4,49; 9,53</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>109,61%</t>
+          <t>115,91%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>102,96%</t>
+          <t>105,52%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 151,46</t>
+          <t>-4,26; 147,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,87; 174,03</t>
+          <t>4,91; 155,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36,82; 234,96</t>
+          <t>46,98; 238,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-53,46; 71,07</t>
+          <t>-54,99; 75,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,16; 108,21</t>
+          <t>-33,8; 117,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,27; 223,47</t>
+          <t>20,59; 212,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,96; 73,59</t>
+          <t>-15,22; 81,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 96,65</t>
+          <t>0,55; 108,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>50,81; 174,08</t>
+          <t>52,83; 182,81</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,82</t>
+          <t>8,04</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,86</t>
+          <t>4,77</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6,55</t>
+          <t>6,58</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 4,52</t>
+          <t>-3,23; 4,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 6,71</t>
+          <t>-1,72; 6,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,55; 12,06</t>
+          <t>3,79; 12,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 5,45</t>
+          <t>-3,07; 5,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 6,08</t>
+          <t>-1,65; 6,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 7,9</t>
+          <t>1,1; 7,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 3,64</t>
+          <t>-1,53; 4,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 5,59</t>
+          <t>-0,76; 5,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,77; 9,56</t>
+          <t>3,87; 9,38</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,53%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-36,85; 74,1</t>
+          <t>-32,94; 77,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,11; 107,84</t>
+          <t>-19,34; 105,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30,49; 200,81</t>
+          <t>34,42; 200,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-30,71; 119,33</t>
+          <t>-39,46; 104,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,65; 134,24</t>
+          <t>-22,3; 137,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,49; 181,85</t>
+          <t>11,2; 178,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,92; 61,82</t>
+          <t>-17,71; 69,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 94,91</t>
+          <t>-8,61; 85,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>39,73; 161,05</t>
+          <t>40,56; 163,51</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>6,77</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,61</t>
+          <t>10,04</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,78</t>
+          <t>7,65</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 7,21</t>
+          <t>-1,02; 7,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 7,47</t>
+          <t>-0,73; 7,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 8,8</t>
+          <t>2,93; 11,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 4,35</t>
+          <t>-6,83; 4,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 11,06</t>
+          <t>-3,55; 11,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,07; 16,46</t>
+          <t>3,67; 16,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 5,23</t>
+          <t>-1,21; 5,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,01; 7,28</t>
+          <t>-0,09; 6,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 9,21</t>
+          <t>3,95; 11,04</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>112,73%</t>
+          <t>106,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>74,98%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 78,12</t>
+          <t>-8,12; 82,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 86,51</t>
+          <t>-7,19; 84,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-58,1; 91,93</t>
+          <t>22,51; 127,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-51,3; 68,78</t>
+          <t>-51,16; 75,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-27,21; 158,99</t>
+          <t>-30,9; 167,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,52; 261,32</t>
+          <t>20,97; 265,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-11,91; 60,97</t>
+          <t>-11,19; 63,91</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,01; 85,13</t>
+          <t>-0,55; 81,93</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-48,12; 95,7</t>
+          <t>33,25; 132,61</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,52</t>
+          <t>6,41</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,39</t>
+          <t>5,0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>14,56</t>
+          <t>5,7</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,82; 6,78</t>
+          <t>1,88; 7,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,9</t>
+          <t>1,35; 6,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,93; 9,13</t>
+          <t>3,77; 8,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 4,94</t>
+          <t>-1,1; 4,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 4,53</t>
+          <t>-1,11; 4,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,35; 58,63</t>
+          <t>2,24; 7,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,48; 5,39</t>
+          <t>1,3; 5,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,65</t>
+          <t>0,89; 4,61</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,15; 36,54</t>
+          <t>4,01; 7,86</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>307,15%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>170,73%</t>
+          <t>66,9%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,9; 83,28</t>
+          <t>18,45; 89,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,57; 72,85</t>
+          <t>12,49; 78,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39,49; 112,7</t>
+          <t>37,07; 112,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-14,83; 82,54</t>
+          <t>-11,15; 79,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 72,79</t>
+          <t>-12,51; 79,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>53,16; 1035,61</t>
+          <t>23,71; 123,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,2; 69,78</t>
+          <t>13,67; 66,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,24; 60,04</t>
+          <t>9,27; 60,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>57,79; 447,27</t>
+          <t>41,67; 101,47</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8,66</t>
+          <t>7,18</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,53</t>
+          <t>11,19</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>9,28</t>
+          <t>9,48</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,1; 9,42</t>
+          <t>0,88; 9,28</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,63; 9,23</t>
+          <t>1,82; 9,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,95; 12,68</t>
+          <t>3,19; 11,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,78; 10,26</t>
+          <t>3,08; 10,78</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,65; 9,26</t>
+          <t>1,35; 9,06</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,01; 13,85</t>
+          <t>7,21; 14,86</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,95; 8,52</t>
+          <t>3,04; 8,97</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,52; 7,89</t>
+          <t>2,5; 7,98</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,65; 12,49</t>
+          <t>6,86; 12,08</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>112,95%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>103,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>98,33%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>9,45; 157,34</t>
+          <t>7,18; 163,14</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>16,45; 171,68</t>
+          <t>15,98; 154,89</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>44,8; 224,53</t>
+          <t>30,48; 189,29</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21,42; 110,69</t>
+          <t>21,63; 118,94</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>12,8; 104,85</t>
+          <t>9,18; 101,42</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,32; 150,21</t>
+          <t>55,54; 171,37</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,45; 103,07</t>
+          <t>25,97; 107,85</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>22,15; 97,29</t>
+          <t>22,96; 97,78</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>54,18; 154,93</t>
+          <t>59,91; 149,31</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>1,19</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,31</t>
+          <t>4,01</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2,95</t>
+          <t>3,05</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 3,51</t>
+          <t>-1,12; 3,2</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 2,51</t>
+          <t>-1,15; 2,88</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 3,73</t>
+          <t>-0,61; 3,95</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,9; 9,23</t>
+          <t>2,42; 8,68</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,17; 6,6</t>
+          <t>0,25; 6,51</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,65; 7,22</t>
+          <t>1,12; 6,81</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,17; 7,17</t>
+          <t>2,28; 7,39</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,14; 5,2</t>
+          <t>0,19; 5,43</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,35</t>
+          <t>0,7; 5,58</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>116,04%</t>
+          <t>121,02%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>27,06%</t>
         </is>
       </c>
     </row>
@@ -1873,37 +1873,37 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-66,81; 1195,5</t>
+          <t>-65,02; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>17,87; 72,66</t>
+          <t>16,14; 70,97</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1,16; 52,21</t>
+          <t>1,5; 50,87</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10,34; 58,13</t>
+          <t>7,46; 54,81</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>17,87; 71,91</t>
+          <t>18,22; 72,54</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 50,28</t>
+          <t>1,26; 53,89</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3,97; 52,21</t>
+          <t>6,33; 55,47</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5,67</t>
+          <t>6,61</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,63</t>
+          <t>5,93</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>8,24</t>
+          <t>6,27</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,9</t>
+          <t>2,1; 4,94</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,96</t>
+          <t>2,17; 4,93</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2,48; 7,41</t>
+          <t>5,21; 8,01</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,88; 5,16</t>
+          <t>1,99; 5,03</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,58</t>
+          <t>1,38; 4,65</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,3; 26,09</t>
+          <t>4,35; 7,23</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,56</t>
+          <t>2,47; 4,61</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,22</t>
+          <t>2,15; 4,33</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5,27; 18,03</t>
+          <t>5,3; 7,38</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>103,1%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>68,72%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>23,07; 68,33</t>
+          <t>25,22; 66,8</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>23,99; 69,18</t>
+          <t>25,39; 67,94</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>31,45; 101,57</t>
+          <t>61,69; 110,9</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>17,1; 54,2</t>
+          <t>18,13; 53,29</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>11,85; 47,79</t>
+          <t>12,34; 47,73</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>49,31; 254,67</t>
+          <t>39,68; 76,24</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,72; 52,23</t>
+          <t>25,4; 52,65</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>21,47; 48,04</t>
+          <t>22,52; 49,86</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>56,18; 199,75</t>
+          <t>54,58; 86,08</t>
         </is>
       </c>
     </row>
